--- a/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-05T15:48:53+00:00</t>
+    <t>2023-07-05T15:49:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -869,7 +869,7 @@
     <t>idNatSt</t>
   </si>
   <si>
-    <t>Une instance par identifiant (FINESS, SIREN, SIRET, idNat_Struct…).</t>
+    <t>Une instance par identifiant idNat_Struct</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>

--- a/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-05T15:49:30+00:00</t>
+    <t>2023-07-05T16:18:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-05T16:18:59+00:00</t>
+    <t>2023-07-08T08:21:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
+++ b/ig/nr-impr-organization-system/StructureDefinition-as-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$146</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3883" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4756" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-08T08:21:48+00:00</t>
+    <t>2023-07-10T15:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -784,7 +784,7 @@
     <t>Organization.identifier.system</t>
   </si>
   <si>
-    <t>Le système doit correspondre à l'idnat struct tel que défini dans l'Annexe Transverse – Source des données métier pour les professionnels et les structures : https://esante.gouv.fr/sites/default/files/media_entity/documents/ci-sis_anx_sources-donnees-professionnels-structures_v1.5_0.pdf</t>
+    <t>The namespace for the identifier value</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -869,7 +869,7 @@
     <t>idNatSt</t>
   </si>
   <si>
-    <t>Une instance par identifiant idNat_Struct</t>
+    <t>Identifiant idNat_Struct qui doit correspondre à l'idnat struct tel que défini dans l'Annexe Transverse – Source des données métier pour les professionnels et les structures : https://esante.gouv.fr/sites/default/files/media_entity/documents/ci-sis_anx_sources-donnees-professionnels-structures_v1.5_0.pdf</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -903,9 +903,6 @@
     <t>Organization.identifier:idNatSt.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
     <t>urn:oid:1.2.250.1.71.4.2.2</t>
   </si>
   <si>
@@ -919,6 +916,114 @@
   </si>
   <si>
     <t>Organization.identifier:idNatSt.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene</t>
+  </si>
+  <si>
+    <t>sirene</t>
+  </si>
+  <si>
+    <t>Identifiant SIREN ou SIRET</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.system</t>
+  </si>
+  <si>
+    <t>http://sirene.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:sirene.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess</t>
+  </si>
+  <si>
+    <t>finess</t>
+  </si>
+  <si>
+    <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.system</t>
+  </si>
+  <si>
+    <t>http://finess.sante.gouv.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:finess.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps</t>
+  </si>
+  <si>
+    <t>adeliRpps</t>
+  </si>
+  <si>
+    <t>Identifiant ADELI rang ou RPPS rang</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.system</t>
+  </si>
+  <si>
+    <t>https://annuaire.sante.fr</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier:adeliRpps.assigner</t>
   </si>
   <si>
     <t>Organization.active</t>
@@ -2051,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ119"/>
+  <dimension ref="A1:AJ146"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.859375" customWidth="true" bestFit="true"/>
@@ -6719,7 +6824,7 @@
         <v>89</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>245</v>
@@ -6738,7 +6843,7 @@
         <v>35</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>248</v>
@@ -6794,7 +6899,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>250</v>
@@ -6823,7 +6928,7 @@
         <v>56</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>252</v>
@@ -6896,7 +7001,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>256</v>
@@ -6998,7 +7103,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>262</v>
@@ -7100,12 +7205,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C50" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="B50" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>35</v>
       </c>
@@ -7114,38 +7221,34 @@
         <v>36</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L50" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="M50" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>291</v>
+        <v>219</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q50" t="s" s="2">
-        <v>292</v>
-      </c>
+      <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
         <v>35</v>
       </c>
@@ -7189,16 +7292,16 @@
         <v>35</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>286</v>
+        <v>215</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>54</v>
+        <v>222</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>81</v>
@@ -7206,10 +7309,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>293</v>
+        <v>223</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7220,32 +7323,28 @@
         <v>36</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>294</v>
+        <v>57</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>35</v>
       </c>
@@ -7269,62 +7368,62 @@
         <v>35</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>298</v>
+        <v>35</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>299</v>
+        <v>35</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>293</v>
+        <v>59</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>35</v>
@@ -7333,23 +7432,21 @@
         <v>35</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>235</v>
+        <v>62</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>303</v>
+        <v>63</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>295</v>
+        <v>64</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>35</v>
       </c>
@@ -7373,31 +7470,31 @@
         <v>35</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>298</v>
+        <v>35</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>293</v>
+        <v>69</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>36</v>
@@ -7409,15 +7506,15 @@
         <v>54</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>307</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7434,22 +7531,26 @@
         <v>35</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>57</v>
+        <v>226</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>35</v>
       </c>
@@ -7473,13 +7574,13 @@
         <v>35</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>35</v>
@@ -7497,7 +7598,7 @@
         <v>35</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>59</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>36</v>
@@ -7506,29 +7607,29 @@
         <v>42</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>35</v>
@@ -7537,21 +7638,23 @@
         <v>35</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>63</v>
+        <v>236</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>64</v>
+        <v>237</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>35</v>
       </c>
@@ -7575,51 +7678,51 @@
         <v>35</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>69</v>
+        <v>242</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>311</v>
+        <v>243</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7642,19 +7745,19 @@
         <v>43</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>313</v>
+        <v>245</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>314</v>
+        <v>246</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>35</v>
@@ -7664,10 +7767,10 @@
         <v>35</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>35</v>
+        <v>293</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>35</v>
@@ -7703,13 +7806,13 @@
         <v>35</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>54</v>
@@ -7720,10 +7823,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>318</v>
+        <v>250</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7731,7 +7834,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>42</v>
@@ -7743,18 +7846,20 @@
         <v>35</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>57</v>
+        <v>251</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -7767,7 +7872,7 @@
         <v>35</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>35</v>
@@ -7803,7 +7908,7 @@
         <v>35</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>36</v>
@@ -7812,29 +7917,29 @@
         <v>42</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>320</v>
+        <v>256</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>35</v>
@@ -7843,19 +7948,19 @@
         <v>35</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>63</v>
+        <v>257</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>64</v>
+        <v>258</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>65</v>
+        <v>259</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7893,39 +7998,39 @@
         <v>35</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>69</v>
+        <v>260</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>70</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7933,7 +8038,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>42</v>
@@ -7948,32 +8053,30 @@
         <v>43</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>89</v>
+        <v>263</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>324</v>
+        <v>265</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>327</v>
+        <v>35</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T58" t="s" s="2">
-        <v>327</v>
+        <v>35</v>
       </c>
       <c r="U58" t="s" s="2">
         <v>35</v>
@@ -8009,7 +8112,7 @@
         <v>35</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>267</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>36</v>
@@ -8021,17 +8124,19 @@
         <v>54</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>35</v>
       </c>
@@ -8040,7 +8145,7 @@
         <v>36</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>35</v>
@@ -8052,18 +8157,18 @@
         <v>43</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>331</v>
+        <v>299</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>35</v>
       </c>
@@ -8111,16 +8216,16 @@
         <v>35</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>334</v>
+        <v>215</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>54</v>
+        <v>222</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>81</v>
@@ -8128,10 +8233,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>336</v>
+        <v>223</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8151,23 +8256,19 @@
         <v>35</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>337</v>
+        <v>57</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>35</v>
       </c>
@@ -8215,7 +8316,7 @@
         <v>35</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>341</v>
+        <v>59</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>36</v>
@@ -8224,29 +8325,29 @@
         <v>42</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>342</v>
+        <v>301</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>224</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>35</v>
@@ -8255,23 +8356,21 @@
         <v>35</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>344</v>
+        <v>63</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>345</v>
+        <v>64</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>35</v>
       </c>
@@ -8307,39 +8406,39 @@
         <v>35</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>347</v>
+        <v>69</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>349</v>
+        <v>225</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8356,25 +8455,25 @@
         <v>35</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J62" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>287</v>
+        <v>123</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>350</v>
+        <v>226</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>351</v>
+        <v>227</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>352</v>
+        <v>228</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>353</v>
+        <v>229</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>35</v>
@@ -8399,13 +8498,13 @@
         <v>35</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>35</v>
@@ -8423,7 +8522,7 @@
         <v>35</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>354</v>
+        <v>233</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>36</v>
@@ -8440,10 +8539,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>356</v>
+        <v>234</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8451,7 +8550,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>42</v>
@@ -8466,19 +8565,19 @@
         <v>43</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>358</v>
+        <v>237</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>359</v>
+        <v>238</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>360</v>
+        <v>239</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>35</v>
@@ -8503,13 +8602,13 @@
         <v>35</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>35</v>
@@ -8527,7 +8626,7 @@
         <v>35</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>361</v>
+        <v>242</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>36</v>
@@ -8544,20 +8643,18 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>362</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>42</v>
@@ -8572,19 +8669,19 @@
         <v>43</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>235</v>
+        <v>89</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>294</v>
+        <v>244</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>296</v>
+        <v>246</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>297</v>
+        <v>247</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>35</v>
@@ -8594,10 +8691,10 @@
         <v>35</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>35</v>
+        <v>305</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>35</v>
@@ -8609,13 +8706,13 @@
         <v>35</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>364</v>
+        <v>35</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>365</v>
+        <v>35</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>35</v>
@@ -8633,13 +8730,13 @@
         <v>35</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>54</v>
@@ -8650,10 +8747,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>366</v>
+        <v>306</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8661,7 +8758,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>42</v>
@@ -8673,18 +8770,20 @@
         <v>35</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>57</v>
+        <v>251</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>35</v>
@@ -8697,7 +8796,7 @@
         <v>35</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>35</v>
@@ -8733,7 +8832,7 @@
         <v>35</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>36</v>
@@ -8742,29 +8841,29 @@
         <v>42</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>367</v>
+        <v>307</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>35</v>
@@ -8773,19 +8872,19 @@
         <v>35</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>63</v>
+        <v>257</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>64</v>
+        <v>258</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>65</v>
+        <v>259</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -8823,39 +8922,39 @@
         <v>35</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>69</v>
+        <v>260</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>70</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>368</v>
+        <v>308</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8863,7 +8962,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>42</v>
@@ -8878,20 +8977,18 @@
         <v>43</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>101</v>
+        <v>263</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>312</v>
+        <v>264</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>313</v>
+        <v>265</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>35</v>
       </c>
@@ -8939,29 +9036,31 @@
         <v>35</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>369</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>35</v>
       </c>
@@ -8970,7 +9069,7 @@
         <v>36</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>35</v>
@@ -8979,19 +9078,21 @@
         <v>35</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>58</v>
+        <v>218</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>35</v>
       </c>
@@ -9039,38 +9140,38 @@
         <v>35</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>35</v>
+        <v>222</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>370</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>320</v>
+        <v>223</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>35</v>
@@ -9082,17 +9183,15 @@
         <v>35</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>35</v>
@@ -9129,50 +9228,50 @@
         <v>35</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>371</v>
+        <v>313</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>35</v>
@@ -9181,35 +9280,33 @@
         <v>35</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>372</v>
+        <v>63</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>372</v>
+        <v>64</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>373</v>
+        <v>35</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>373</v>
+        <v>35</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>35</v>
@@ -9233,39 +9330,39 @@
         <v>35</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>328</v>
+        <v>69</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>330</v>
+        <v>225</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9282,24 +9379,26 @@
         <v>35</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>331</v>
+        <v>226</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>332</v>
+        <v>227</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>35</v>
       </c>
@@ -9323,13 +9422,13 @@
         <v>35</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>35</v>
+        <v>231</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>35</v>
@@ -9347,7 +9446,7 @@
         <v>35</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>334</v>
+        <v>233</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>36</v>
@@ -9364,10 +9463,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>336</v>
+        <v>234</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9375,7 +9474,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>42</v>
@@ -9390,19 +9489,19 @@
         <v>43</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>123</v>
+        <v>235</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>337</v>
+        <v>236</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>338</v>
+        <v>237</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>339</v>
+        <v>238</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>340</v>
+        <v>239</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>35</v>
@@ -9427,13 +9526,13 @@
         <v>35</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>35</v>
+        <v>240</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>35</v>
@@ -9451,7 +9550,7 @@
         <v>35</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>341</v>
+        <v>242</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>36</v>
@@ -9468,10 +9567,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>376</v>
+        <v>316</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>343</v>
+        <v>243</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9479,7 +9578,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>42</v>
@@ -9494,19 +9593,19 @@
         <v>43</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>344</v>
+        <v>244</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>345</v>
+        <v>245</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>339</v>
+        <v>246</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>346</v>
+        <v>247</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>35</v>
@@ -9516,10 +9615,10 @@
         <v>35</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>35</v>
+        <v>317</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>35</v>
+        <v>248</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>35</v>
@@ -9555,7 +9654,7 @@
         <v>35</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>347</v>
+        <v>249</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>36</v>
@@ -9572,10 +9671,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>349</v>
+        <v>250</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9583,7 +9682,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>42</v>
@@ -9598,20 +9697,18 @@
         <v>43</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>287</v>
+        <v>56</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>350</v>
+        <v>251</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>351</v>
+        <v>252</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>35</v>
       </c>
@@ -9623,7 +9720,7 @@
         <v>35</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>35</v>
+        <v>254</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>35</v>
@@ -9659,7 +9756,7 @@
         <v>35</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>354</v>
+        <v>255</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>36</v>
@@ -9676,10 +9773,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>356</v>
+        <v>256</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9702,20 +9799,18 @@
         <v>43</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>56</v>
+        <v>175</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>357</v>
+        <v>257</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>358</v>
+        <v>258</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>35</v>
       </c>
@@ -9763,7 +9858,7 @@
         <v>35</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>361</v>
+        <v>260</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>36</v>
@@ -9775,19 +9870,17 @@
         <v>54</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>35</v>
       </c>
@@ -9808,20 +9901,18 @@
         <v>43</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>235</v>
+        <v>263</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>294</v>
+        <v>264</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>35</v>
       </c>
@@ -9845,13 +9936,13 @@
         <v>35</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>381</v>
+        <v>35</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>382</v>
+        <v>35</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>35</v>
@@ -9869,27 +9960,27 @@
         <v>35</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9903,29 +9994,35 @@
         <v>42</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>56</v>
+        <v>322</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>57</v>
+        <v>323</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="Q77" s="2"/>
+      <c r="Q77" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="R77" t="s" s="2">
         <v>35</v>
       </c>
@@ -9969,7 +10066,7 @@
         <v>35</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>59</v>
+        <v>321</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>36</v>
@@ -9978,22 +10075,22 @@
         <v>42</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>384</v>
+        <v>328</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10003,27 +10100,29 @@
         <v>37</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>63</v>
+        <v>329</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>64</v>
+        <v>330</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>35</v>
       </c>
@@ -10047,23 +10146,21 @@
         <v>35</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>35</v>
+        <v>333</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>35</v>
+        <v>334</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>67</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
         <v>35</v>
       </c>
@@ -10071,7 +10168,7 @@
         <v>68</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>69</v>
+        <v>328</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>36</v>
@@ -10083,23 +10180,25 @@
         <v>54</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>35</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>42</v>
@@ -10114,19 +10213,19 @@
         <v>43</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>35</v>
@@ -10151,13 +10250,13 @@
         <v>35</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>35</v>
+        <v>333</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>35</v>
+        <v>340</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>35</v>
@@ -10175,7 +10274,7 @@
         <v>35</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>36</v>
@@ -10192,10 +10291,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>386</v>
+        <v>341</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10292,10 +10391,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>387</v>
+        <v>343</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10394,10 +10493,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>388</v>
+        <v>345</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10420,26 +10519,26 @@
         <v>43</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>389</v>
+        <v>347</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>390</v>
+        <v>35</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>35</v>
@@ -10481,13 +10580,13 @@
         <v>35</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>54</v>
@@ -10498,10 +10597,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>391</v>
+        <v>352</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10521,20 +10620,18 @@
         <v>35</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>331</v>
+        <v>57</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>35</v>
@@ -10583,7 +10680,7 @@
         <v>35</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>334</v>
+        <v>59</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>36</v>
@@ -10592,29 +10689,29 @@
         <v>42</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>35</v>
@@ -10623,23 +10720,21 @@
         <v>35</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>337</v>
+        <v>63</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>338</v>
+        <v>64</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>35</v>
       </c>
@@ -10675,39 +10770,39 @@
         <v>35</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>341</v>
+        <v>69</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>393</v>
+        <v>356</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10715,7 +10810,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>42</v>
@@ -10730,32 +10825,32 @@
         <v>43</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>35</v>
+        <v>362</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>35</v>
+        <v>362</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>35</v>
@@ -10791,7 +10886,7 @@
         <v>35</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>36</v>
@@ -10808,10 +10903,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10834,20 +10929,18 @@
         <v>43</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>287</v>
+        <v>56</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>35</v>
       </c>
@@ -10895,7 +10988,7 @@
         <v>35</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>36</v>
@@ -10912,10 +11005,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10938,19 +11031,19 @@
         <v>43</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>35</v>
@@ -10999,7 +11092,7 @@
         <v>35</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>36</v>
@@ -11016,14 +11109,12 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>35</v>
       </c>
@@ -11032,7 +11123,7 @@
         <v>36</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>35</v>
@@ -11044,19 +11135,19 @@
         <v>43</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>295</v>
+        <v>380</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>399</v>
+        <v>374</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>297</v>
+        <v>381</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>35</v>
@@ -11081,11 +11172,13 @@
         <v>35</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y88" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z88" t="s" s="2">
-        <v>400</v>
+        <v>35</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>35</v>
@@ -11103,13 +11196,13 @@
         <v>35</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>293</v>
+        <v>382</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>54</v>
@@ -11120,14 +11213,12 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C89" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>35</v>
       </c>
@@ -11136,7 +11227,7 @@
         <v>36</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>35</v>
@@ -11148,19 +11239,19 @@
         <v>43</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>295</v>
+        <v>386</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>297</v>
+        <v>388</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>35</v>
@@ -11185,11 +11276,13 @@
         <v>35</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y89" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z89" t="s" s="2">
-        <v>405</v>
+        <v>35</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>35</v>
@@ -11207,13 +11300,13 @@
         <v>35</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>293</v>
+        <v>389</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>54</v>
@@ -11224,14 +11317,12 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>35</v>
       </c>
@@ -11240,7 +11331,7 @@
         <v>36</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>35</v>
@@ -11252,19 +11343,19 @@
         <v>43</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>235</v>
+        <v>56</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>295</v>
+        <v>393</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>297</v>
+        <v>395</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>35</v>
@@ -11289,11 +11380,13 @@
         <v>35</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>35</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>410</v>
+        <v>35</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>35</v>
@@ -11311,13 +11404,13 @@
         <v>35</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>293</v>
+        <v>396</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>54</v>
@@ -11328,12 +11421,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="D91" t="s" s="2">
         <v>35</v>
       </c>
@@ -11345,7 +11440,7 @@
         <v>42</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>35</v>
@@ -11354,19 +11449,19 @@
         <v>43</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>56</v>
+        <v>235</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>412</v>
+        <v>329</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>413</v>
+        <v>330</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>414</v>
+        <v>331</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>415</v>
+        <v>332</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>35</v>
@@ -11391,13 +11486,13 @@
         <v>35</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>35</v>
+        <v>399</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>35</v>
+        <v>400</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>35</v>
@@ -11415,16 +11510,16 @@
         <v>35</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>411</v>
+        <v>328</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>222</v>
+        <v>54</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>81</v>
@@ -11432,10 +11527,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>416</v>
+        <v>342</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11446,10 +11541,10 @@
         <v>36</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>35</v>
@@ -11461,17 +11556,13 @@
         <v>56</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>417</v>
+        <v>57</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>35</v>
       </c>
@@ -11519,31 +11610,31 @@
         <v>35</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>416</v>
+        <v>59</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>421</v>
+        <v>344</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -11553,7 +11644,7 @@
         <v>37</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>35</v>
@@ -11562,20 +11653,18 @@
         <v>35</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>422</v>
+        <v>62</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>423</v>
+        <v>63</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>424</v>
+        <v>64</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>35</v>
       </c>
@@ -11611,9 +11700,11 @@
         <v>35</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AC93" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>67</v>
+      </c>
       <c r="AD93" t="s" s="2">
         <v>35</v>
       </c>
@@ -11621,7 +11712,7 @@
         <v>68</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>421</v>
+        <v>69</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>36</v>
@@ -11630,18 +11721,18 @@
         <v>37</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>428</v>
+        <v>54</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>429</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>430</v>
+        <v>346</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11649,7 +11740,7 @@
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G94" t="s" s="2">
         <v>42</v>
@@ -11661,19 +11752,23 @@
         <v>35</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>57</v>
+        <v>347</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>35</v>
       </c>
@@ -11721,38 +11816,38 @@
         <v>35</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>59</v>
+        <v>351</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>431</v>
+        <v>404</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>431</v>
+        <v>353</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>35</v>
@@ -11764,17 +11859,15 @@
         <v>35</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>65</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>35</v>
@@ -11811,43 +11904,41 @@
         <v>35</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>61</v>
       </c>
@@ -11856,7 +11947,7 @@
         <v>36</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>35</v>
@@ -11868,13 +11959,13 @@
         <v>35</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>434</v>
+        <v>62</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>435</v>
+        <v>63</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>65</v>
@@ -11915,16 +12006,16 @@
         <v>35</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF96" t="s" s="2">
         <v>69</v>
@@ -11944,10 +12035,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>436</v>
+        <v>357</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11970,30 +12061,32 @@
         <v>43</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>437</v>
+        <v>407</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>35</v>
+        <v>408</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>35</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>35</v>
+        <v>408</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>35</v>
@@ -12005,13 +12098,13 @@
         <v>35</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>440</v>
+        <v>35</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>441</v>
+        <v>35</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>35</v>
@@ -12029,7 +12122,7 @@
         <v>35</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>442</v>
+        <v>363</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>36</v>
@@ -12038,7 +12131,7 @@
         <v>42</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>443</v>
+        <v>54</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>81</v>
@@ -12046,10 +12139,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>444</v>
+        <v>365</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12057,7 +12150,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>42</v>
@@ -12075,17 +12168,15 @@
         <v>56</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>445</v>
+        <v>366</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>446</v>
+        <v>367</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>35</v>
       </c>
@@ -12133,7 +12224,7 @@
         <v>35</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>449</v>
+        <v>369</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>36</v>
@@ -12150,10 +12241,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>450</v>
+        <v>371</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12170,7 +12261,7 @@
         <v>35</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>43</v>
@@ -12179,16 +12270,16 @@
         <v>123</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>451</v>
+        <v>372</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>452</v>
+        <v>373</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>453</v>
+        <v>374</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>454</v>
+        <v>375</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>35</v>
@@ -12213,13 +12304,13 @@
         <v>35</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>230</v>
+        <v>35</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>455</v>
+        <v>35</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>456</v>
+        <v>35</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>35</v>
@@ -12237,7 +12328,7 @@
         <v>35</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>457</v>
+        <v>376</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>36</v>
@@ -12254,10 +12345,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>458</v>
+        <v>411</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>458</v>
+        <v>378</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12280,18 +12371,20 @@
         <v>43</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>459</v>
+        <v>56</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>460</v>
+        <v>379</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>461</v>
+        <v>380</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O100" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>35</v>
       </c>
@@ -12339,7 +12432,7 @@
         <v>35</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>463</v>
+        <v>382</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>36</v>
@@ -12356,10 +12449,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>464</v>
+        <v>412</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>464</v>
+        <v>384</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12382,18 +12475,20 @@
         <v>43</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>175</v>
+        <v>322</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>465</v>
+        <v>385</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>466</v>
+        <v>386</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>35</v>
       </c>
@@ -12441,7 +12536,7 @@
         <v>35</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>468</v>
+        <v>389</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>36</v>
@@ -12453,19 +12548,17 @@
         <v>54</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>261</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>469</v>
+        <v>413</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>35</v>
       </c>
@@ -12474,31 +12567,31 @@
         <v>36</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H102" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J102" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="I102" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K102" t="s" s="2">
-        <v>471</v>
+        <v>56</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>472</v>
+        <v>392</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>35</v>
@@ -12547,29 +12640,31 @@
         <v>35</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>429</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>473</v>
+        <v>414</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C103" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="D103" t="s" s="2">
         <v>35</v>
       </c>
@@ -12578,31 +12673,31 @@
         <v>36</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H103" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J103" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="I103" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>35</v>
-      </c>
       <c r="K103" t="s" s="2">
-        <v>474</v>
+        <v>235</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>475</v>
+        <v>329</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>476</v>
+        <v>330</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>477</v>
+        <v>331</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>478</v>
+        <v>332</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>35</v>
@@ -12627,13 +12722,13 @@
         <v>35</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>35</v>
+        <v>230</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>35</v>
+        <v>416</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>35</v>
+        <v>417</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>35</v>
@@ -12651,7 +12746,7 @@
         <v>35</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>473</v>
+        <v>328</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>36</v>
@@ -12663,15 +12758,15 @@
         <v>54</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>479</v>
+        <v>81</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>480</v>
+        <v>418</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>480</v>
+        <v>342</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12691,23 +12786,19 @@
         <v>35</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>481</v>
+        <v>56</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>482</v>
+        <v>57</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>35</v>
       </c>
@@ -12755,7 +12846,7 @@
         <v>35</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>480</v>
+        <v>59</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>36</v>
@@ -12764,29 +12855,29 @@
         <v>42</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>268</v>
+        <v>35</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>486</v>
+        <v>419</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>486</v>
+        <v>344</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>35</v>
@@ -12798,15 +12889,17 @@
         <v>35</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>65</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>35</v>
@@ -12843,50 +12936,50 @@
         <v>35</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>420</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>487</v>
+        <v>346</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>35</v>
@@ -12895,21 +12988,23 @@
         <v>35</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>63</v>
+        <v>347</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>64</v>
+        <v>348</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>35</v>
       </c>
@@ -12945,19 +13040,19 @@
         <v>35</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>69</v>
+        <v>351</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>36</v>
@@ -12969,15 +13064,15 @@
         <v>54</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>488</v>
+        <v>421</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>488</v>
+        <v>353</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12997,20 +13092,18 @@
         <v>35</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>489</v>
+        <v>57</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>35</v>
@@ -13059,7 +13152,7 @@
         <v>35</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>492</v>
+        <v>59</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>36</v>
@@ -13068,29 +13161,29 @@
         <v>42</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>493</v>
+        <v>35</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>81</v>
+        <v>35</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>494</v>
+        <v>422</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>494</v>
+        <v>355</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>35</v>
@@ -13099,19 +13192,19 @@
         <v>35</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>495</v>
+        <v>63</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>496</v>
+        <v>64</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>497</v>
+        <v>65</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13137,51 +13230,51 @@
         <v>35</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>498</v>
+        <v>35</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>305</v>
+        <v>35</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>499</v>
+        <v>69</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>500</v>
+        <v>423</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>500</v>
+        <v>357</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13189,7 +13282,7 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>42</v>
@@ -13204,24 +13297,26 @@
         <v>43</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>501</v>
+        <v>424</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>502</v>
+        <v>424</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>35</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>35</v>
+        <v>425</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>35</v>
@@ -13263,7 +13358,7 @@
         <v>35</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>504</v>
+        <v>363</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>36</v>
@@ -13280,10 +13375,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>505</v>
+        <v>426</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>505</v>
+        <v>365</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13309,13 +13404,13 @@
         <v>56</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>506</v>
+        <v>366</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>507</v>
+        <v>367</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>508</v>
+        <v>368</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13365,7 +13460,7 @@
         <v>35</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>509</v>
+        <v>369</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>36</v>
@@ -13382,10 +13477,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>510</v>
+        <v>427</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>510</v>
+        <v>371</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13396,7 +13491,7 @@
         <v>36</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>35</v>
@@ -13405,22 +13500,22 @@
         <v>35</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>511</v>
+        <v>123</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>512</v>
+        <v>372</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>513</v>
+        <v>373</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>514</v>
+        <v>374</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>515</v>
+        <v>375</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>35</v>
@@ -13469,13 +13564,13 @@
         <v>35</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>510</v>
+        <v>376</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>54</v>
@@ -13486,10 +13581,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>516</v>
+        <v>428</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>516</v>
+        <v>378</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13509,19 +13604,23 @@
         <v>35</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>56</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>57</v>
+        <v>379</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>35</v>
       </c>
@@ -13569,7 +13668,7 @@
         <v>35</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>59</v>
+        <v>382</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>36</v>
@@ -13578,29 +13677,29 @@
         <v>42</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>517</v>
+        <v>429</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>517</v>
+        <v>384</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>35</v>
@@ -13609,21 +13708,23 @@
         <v>35</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>62</v>
+        <v>322</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>63</v>
+        <v>385</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>64</v>
+        <v>386</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>35</v>
       </c>
@@ -13659,74 +13760,74 @@
         <v>35</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>69</v>
+        <v>389</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>518</v>
+        <v>430</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>518</v>
+        <v>391</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>519</v>
+        <v>35</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>35</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>43</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>520</v>
+        <v>392</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>521</v>
+        <v>393</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>65</v>
+        <v>394</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>213</v>
+        <v>395</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>35</v>
@@ -13775,29 +13876,31 @@
         <v>35</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>522</v>
+        <v>396</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>54</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>523</v>
+        <v>431</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C115" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="D115" t="s" s="2">
         <v>35</v>
       </c>
@@ -13806,7 +13909,7 @@
         <v>36</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>35</v>
@@ -13815,22 +13918,22 @@
         <v>35</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>235</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>524</v>
+        <v>433</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>525</v>
+        <v>330</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>526</v>
+        <v>434</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>527</v>
+        <v>332</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>35</v>
@@ -13855,13 +13958,11 @@
         <v>35</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>529</v>
+        <v>435</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>35</v>
@@ -13879,13 +13980,13 @@
         <v>35</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>523</v>
+        <v>328</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>54</v>
@@ -13896,12 +13997,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>530</v>
+        <v>436</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C116" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="D116" t="s" s="2">
         <v>35</v>
       </c>
@@ -13910,7 +14013,7 @@
         <v>36</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>35</v>
@@ -13919,22 +14022,22 @@
         <v>35</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>531</v>
+        <v>235</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>532</v>
+        <v>438</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>533</v>
+        <v>330</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>534</v>
+        <v>439</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>535</v>
+        <v>332</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>35</v>
@@ -13959,13 +14062,11 @@
         <v>35</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>35</v>
+        <v>440</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>35</v>
@@ -13983,13 +14084,13 @@
         <v>35</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>530</v>
+        <v>328</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>54</v>
@@ -14000,12 +14101,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>536</v>
+        <v>441</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>35</v>
       </c>
@@ -14023,20 +14126,22 @@
         <v>35</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>422</v>
+        <v>235</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O117" t="s" s="2">
-        <v>537</v>
+        <v>332</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>35</v>
@@ -14061,13 +14166,11 @@
         <v>35</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>35</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>35</v>
+        <v>445</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>35</v>
@@ -14085,7 +14188,7 @@
         <v>35</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>536</v>
+        <v>328</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>36</v>
@@ -14097,15 +14200,15 @@
         <v>54</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>538</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>539</v>
+        <v>446</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>539</v>
+        <v>446</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14119,28 +14222,28 @@
         <v>42</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>35</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>540</v>
+        <v>56</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>541</v>
+        <v>447</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>476</v>
+        <v>448</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>542</v>
+        <v>449</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>543</v>
+        <v>450</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>35</v>
@@ -14189,7 +14292,7 @@
         <v>35</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>539</v>
+        <v>446</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>36</v>
@@ -14198,7 +14301,7 @@
         <v>42</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>54</v>
+        <v>222</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>81</v>
@@ -14206,10 +14309,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>544</v>
+        <v>451</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>544</v>
+        <v>451</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14232,19 +14335,19 @@
         <v>35</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>545</v>
+        <v>56</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>546</v>
+        <v>452</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>547</v>
+        <v>453</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>548</v>
+        <v>454</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>549</v>
+        <v>455</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>35</v>
@@ -14293,7 +14396,7 @@
         <v>35</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>544</v>
+        <v>451</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>36</v>
@@ -14305,11 +14408,2785 @@
         <v>54</v>
       </c>
       <c r="AJ119" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AC120" s="2"/>
+      <c r="AD120" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="D123" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="126" hidden="true">
+      <c r="A126" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E126" s="2"/>
+      <c r="F126" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q126" s="2"/>
+      <c r="R126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E127" s="2"/>
+      <c r="F127" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J127" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K127" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L127" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O127" s="2"/>
+      <c r="P127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q127" s="2"/>
+      <c r="R127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="D129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="P131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="140" hidden="true">
+      <c r="A140" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" hidden="true">
+      <c r="A141" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="P141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" hidden="true">
+      <c r="A142" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="P142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="143" hidden="true">
+      <c r="A143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="P143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" hidden="true">
+      <c r="A144" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="P144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="145" hidden="true">
+      <c r="A145" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="P145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="146" hidden="true">
+      <c r="A146" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O146" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="P146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
         <v>268</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ119">
+  <autoFilter ref="A1:AJ146">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14319,7 +17196,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI118">
+  <conditionalFormatting sqref="A2:AI145">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
